--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/abr-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/abr-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>10274.7</v>
+        <v>9947.07</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6502.77</v>
+        <v>6295.42</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1727.87</v>
+        <v>1672.78</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>784.4</v>
+        <v>759.39</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2759.67</v>
+        <v>2671.67</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2501.02</v>
+        <v>2421.27</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2653.73</v>
+        <v>2569.11</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10615.81</v>
+        <v>10277.3</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1948.27</v>
+        <v>1886.15</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>9158.18</v>
+        <v>8866.16</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>794.95</v>
+        <v>769.6</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3208.52</v>
+        <v>3106.21</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2324.3</v>
+        <v>2250.18</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3641.75</v>
+        <v>3525.63</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>829.49</v>
+        <v>803.04</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3330.47</v>
+        <v>3264.79</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>15592.7</v>
+        <v>15285.19</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4924.48</v>
+        <v>4827.36</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>9622.110000000001</v>
+        <v>9432.35</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1894.02</v>
+        <v>1856.66</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>15158.96</v>
+        <v>14860.01</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2423.77</v>
+        <v>2375.97</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>4868.75</v>
+        <v>4772.74</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>13108.86</v>
+        <v>12850.34</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1421.46</v>
+        <v>1393.43</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>17259.39</v>
+        <v>16919.01</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2134.93</v>
+        <v>2092.82</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1134.65</v>
+        <v>1112.28</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1112.78</v>
+        <v>1090.83</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>881.35</v>
+        <v>863.97</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2358.26</v>
+        <v>2311.75</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>787.72</v>
+        <v>772.1799999999999</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>38506.95</v>
+        <v>37747.54</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>778.78</v>
+        <v>763.42</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>5682.59</v>
+        <v>5570.53</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>16673.91</v>
+        <v>16345.08</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>8100.1</v>
+        <v>7940.35</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4530.95</v>
+        <v>4441.6</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1703.47</v>
+        <v>1669.87</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>7165.05</v>
+        <v>7023.74</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1424.41</v>
+        <v>1396.32</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1246.62</v>
+        <v>1222.04</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1127.9</v>
+        <v>1105.65</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>841.4400000000001</v>
+        <v>824.85</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>5008.43</v>
+        <v>4876.55</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>780.08</v>
+        <v>759.53</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2004.66</v>
+        <v>1951.87</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>9731.84</v>
+        <v>9475.57</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>825.1</v>
+        <v>803.38</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>918.52</v>
+        <v>894.33</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1338.57</v>
+        <v>1303.32</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>4291.33</v>
+        <v>4178.33</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>11133.93</v>
+        <v>10840.73</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>12212.25</v>
+        <v>11890.66</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5086.9</v>
+        <v>4952.95</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>16494.79</v>
+        <v>16060.43</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>14260.09</v>
+        <v>13884.57</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3733.47</v>
+        <v>3635.15</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2924.81</v>
+        <v>2871.77</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3629</v>
+        <v>3563.19</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>8710.360000000001</v>
+        <v>8552.4</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>779.97</v>
+        <v>765.83</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>3086.29</v>
+        <v>3030.32</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>4172.2</v>
+        <v>4096.53</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2476.39</v>
+        <v>2431.48</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1665.83</v>
+        <v>1635.62</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>22106.59</v>
+        <v>21705.69</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1781.88</v>
+        <v>1749.56</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>5821.1</v>
+        <v>5665.23</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>69051.07000000001</v>
+        <v>67202.12</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2310.05</v>
+        <v>2248.2</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2018.97</v>
+        <v>1964.91</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3187.86</v>
+        <v>3102.5</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>955.98</v>
+        <v>930.38</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>16290.92</v>
+        <v>15854.7</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1473.03</v>
+        <v>1433.59</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1423.09</v>
+        <v>1384.98</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>10127.41</v>
+        <v>9856.23</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>4785.52</v>
+        <v>4657.38</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1602.33</v>
+        <v>1559.43</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2381.03</v>
+        <v>2317.28</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1086.51</v>
+        <v>1057.42</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>38354.49</v>
+        <v>37327.48</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2580.42</v>
+        <v>2511.33</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2025.11</v>
+        <v>1970.89</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>8088.59</v>
+        <v>7872</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1527.24</v>
+        <v>1486.35</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>17262.31</v>
+        <v>17312.57</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1074.73</v>
+        <v>1077.86</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1113.01</v>
+        <v>1116.25</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1396.92</v>
+        <v>1400.99</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1721.87</v>
+        <v>1726.88</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3975.85</v>
+        <v>3987.42</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>4652.86</v>
+        <v>4666.4</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>13235.79</v>
+        <v>13274.32</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2666.67</v>
+        <v>2674.44</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>798.89</v>
+        <v>801.21</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1102.77</v>
+        <v>1105.98</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2411.88</v>
+        <v>2418.91</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1691.79</v>
+        <v>1698.82</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1095.91</v>
+        <v>1100.46</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1021.57</v>
+        <v>1025.81</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>5831.96</v>
+        <v>5856.19</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1421.99</v>
+        <v>1427.9</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1597.19</v>
+        <v>1603.83</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>4765.26</v>
+        <v>4785.06</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>63765.23</v>
+        <v>64030.24</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>12137.54</v>
+        <v>12187.98</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2895.84</v>
+        <v>2907.88</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>783.1900000000001</v>
+        <v>786.45</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>860.45</v>
+        <v>867.75</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>902.02</v>
+        <v>909.6799999999999</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3331.87</v>
+        <v>3360.15</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>5437.19</v>
+        <v>5483.33</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>783.5700000000001</v>
+        <v>790.22</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2987.38</v>
+        <v>3012.74</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1876.67</v>
+        <v>1892.6</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>3801.06</v>
+        <v>3833.32</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>7496.11</v>
+        <v>7559.73</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>11656.44</v>
+        <v>11755.37</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>921.21</v>
+        <v>929.03</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2780.34</v>
+        <v>2803.93</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>821.02</v>
+        <v>827.98</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>7326.23</v>
+        <v>7388.4</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1689.04</v>
+        <v>1703.37</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>11298.44</v>
+        <v>11394.33</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>5128</v>
+        <v>5171.52</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>5112.64</v>
+        <v>5156.03</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>863.95</v>
+        <v>871.29</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>4628.47</v>
+        <v>4620.73</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1680.61</v>
+        <v>1677.8</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2300.99</v>
+        <v>2297.14</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1346.37</v>
+        <v>1344.12</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>9040.48</v>
+        <v>9025.370000000001</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>7768.98</v>
+        <v>7755.99</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1680.61</v>
+        <v>1677.8</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>11527.07</v>
+        <v>11507.79</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>45341.7</v>
+        <v>45265.89</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>4272.12</v>
+        <v>4264.98</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>3349.11</v>
+        <v>3343.51</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1851.95</v>
+        <v>1848.85</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1265.56</v>
+        <v>1263.44</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>5773.41</v>
+        <v>5763.76</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>22429.85</v>
+        <v>22392.35</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>71741.81</v>
+        <v>71621.85000000001</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1447.81</v>
+        <v>1445.39</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1852.39</v>
+        <v>1849.29</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>7782.37</v>
+        <v>7878.15</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2895.14</v>
+        <v>2930.77</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>786.95</v>
+        <v>796.63</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1002.7</v>
+        <v>1015.04</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>797.67</v>
+        <v>807.49</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>2875.31</v>
+        <v>2910.7</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>2158.84</v>
+        <v>2185.41</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>779.96</v>
+        <v>789.5599999999999</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1737.28</v>
+        <v>1758.66</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>918.15</v>
+        <v>929.45</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>11999.05</v>
+        <v>12146.73</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>6548.71</v>
+        <v>6629.31</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1771.31</v>
+        <v>1793.11</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>48796.48</v>
+        <v>49397.04</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>3342.39</v>
+        <v>3383.52</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>33417.97</v>
+        <v>33829.26</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>5223.57</v>
+        <v>5287.86</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2540.64</v>
+        <v>2571.91</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>3210.52</v>
+        <v>3250.03</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>996.42</v>
+        <v>1008.68</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1271.99</v>
+        <v>1287.65</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2118.39</v>
+        <v>2144.46</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>3082.07</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>6184.75</v>
+        <v>6260.87</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>8349.790000000001</v>
+        <v>8452.549999999999</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1783.65</v>
+        <v>1805.6</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2895.54</v>
+        <v>2931.18</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>13604.24</v>
+        <v>13771.67</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>4823.16</v>
+        <v>4882.52</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>2482.95</v>
+        <v>2513.51</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>8349.790000000001</v>
+        <v>8452.549999999999</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>2035.71</v>
+        <v>2062.82</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>6417.02</v>
+        <v>6502.45</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>19774.13</v>
+        <v>20037.38</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>38119.29</v>
+        <v>38626.75</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>814.4299999999999</v>
+        <v>825.27</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>3455.28</v>
+        <v>3501.28</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1924.58</v>
+        <v>1950.2</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>8568.639999999999</v>
+        <v>8682.709999999999</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>11876.3</v>
+        <v>12034.4</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2526.35</v>
+        <v>2559.99</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1669.91</v>
+        <v>1692.14</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>3444.43</v>
+        <v>3490.28</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>874.42</v>
+        <v>886.0599999999999</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1991.21</v>
+        <v>2017.19</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>4251</v>
+        <v>4306.48</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>7947.02</v>
+        <v>8050.73</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>3505.25</v>
+        <v>3550.99</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2798.47</v>
+        <v>2834.99</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2425.85</v>
+        <v>2457.51</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>9690.52</v>
+        <v>9816.98</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>18750.87</v>
+        <v>18995.56</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2045.44</v>
+        <v>2072.13</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1049.82</v>
+        <v>1063.52</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>37374.45</v>
+        <v>37862.17</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>3497.29</v>
+        <v>3542.93</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>41207.32</v>
+        <v>41745.06</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>4118.43</v>
+        <v>4172.17</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>860.83</v>
+        <v>872.0700000000001</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>15739.23</v>
+        <v>15944.62</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>2775.78</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>2883.57</v>
+        <v>2954.54</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>14375.9</v>
+        <v>14729.69</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1112.03</v>
+        <v>1139.4</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1669.69</v>
+        <v>1710.78</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>14015.19</v>
+        <v>14360.1</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>2215.46</v>
+        <v>2269.98</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>7777.73</v>
+        <v>7969.14</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>12219.99</v>
+        <v>12520.73</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>6835.28</v>
+        <v>6964.56</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>7368.86</v>
+        <v>7508.23</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>4175.93</v>
+        <v>4254.9</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>3584.29</v>
+        <v>3652.08</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1056.32</v>
+        <v>1076.29</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2249.37</v>
+        <v>2291.91</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>54231.54</v>
+        <v>55257.2</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>2947.55</v>
+        <v>3003.29</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>931.34</v>
+        <v>948.95</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2799.11</v>
+        <v>2852.05</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1223.48</v>
+        <v>1246.62</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>36756.84</v>
+        <v>37452.01</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1722.14</v>
+        <v>1754.71</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>2104.37</v>
+        <v>2144.17</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>6922.41</v>
+        <v>7053.34</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1163.3</v>
+        <v>1185.3</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>994.99</v>
+        <v>1013.81</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>4183.17</v>
+        <v>4262.28</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>8274.07</v>
+        <v>8430.549999999999</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>3469.59</v>
+        <v>3535.21</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>7214.61</v>
+        <v>7351.06</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>3570.45</v>
+        <v>3611.06</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>4932.4</v>
+        <v>4988.49</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>5007.65</v>
+        <v>5064.59</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>1683.4</v>
+        <v>1702.54</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>3473.97</v>
+        <v>3513.48</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>12325.62</v>
+        <v>12465.79</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>5301.26</v>
+        <v>5361.55</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>3785.16</v>
+        <v>3828.2</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>3960.1</v>
+        <v>4005.14</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>3753.08</v>
+        <v>3795.76</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>22304.02</v>
+        <v>22557.67</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>2915.74</v>
+        <v>2948.9</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>931.65</v>
+        <v>942.25</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>3732.3</v>
+        <v>3774.75</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>837.27</v>
+        <v>846.79</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1831.28</v>
+        <v>1852.11</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1008.33</v>
+        <v>1019.8</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>14538.56</v>
+        <v>14703.9</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>22908.57</v>
+        <v>23169.09</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1764.21</v>
+        <v>1780.1</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>5072.3</v>
+        <v>5118</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>4776.55</v>
+        <v>4819.58</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>989.8099999999999</v>
+        <v>998.72</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>18136.68</v>
+        <v>18300.06</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>9345</v>
+        <v>9429.190000000001</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>9309.33</v>
+        <v>9393.190000000001</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>16705.9</v>
+        <v>16856.39</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>5660.92</v>
+        <v>5711.92</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>6684.99</v>
+        <v>6745.21</v>
       </c>
     </row>
     <row r="283">
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>138463.74</v>
+        <v>139711.06</v>
       </c>
     </row>
     <row r="284">
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>2597.13</v>
+        <v>2620.52</v>
       </c>
     </row>
     <row r="285">
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>786.77</v>
+        <v>793.86</v>
       </c>
     </row>
     <row r="286">
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>5604.04</v>
+        <v>5654.52</v>
       </c>
     </row>
     <row r="287">
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>3381.37</v>
+        <v>3411.84</v>
       </c>
     </row>
     <row r="288">
@@ -18019,7 +18019,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>5873.18</v>
+        <v>5926.09</v>
       </c>
     </row>
     <row r="289">
@@ -18080,7 +18080,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>20566.68</v>
+        <v>20751.95</v>
       </c>
     </row>
     <row r="290">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>947.08</v>
+        <v>955.62</v>
       </c>
     </row>
     <row r="291">
@@ -18202,7 +18202,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1509.26</v>
+        <v>1522.86</v>
       </c>
     </row>
     <row r="292">
@@ -18263,7 +18263,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>43552.79</v>
+        <v>43945.12</v>
       </c>
     </row>
     <row r="293">
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>5205.95</v>
+        <v>5252.85</v>
       </c>
     </row>
     <row r="294">
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>11161.22</v>
+        <v>11261.76</v>
       </c>
     </row>
     <row r="295">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>6723.66</v>
+        <v>6784.23</v>
       </c>
     </row>
     <row r="296">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>6972.93</v>
+        <v>7035.74</v>
       </c>
     </row>
     <row r="297">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>8749.33</v>
+        <v>8805.290000000001</v>
       </c>
     </row>
     <row r="298">
@@ -18629,7 +18629,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>37705.7</v>
+        <v>37946.86</v>
       </c>
     </row>
     <row r="299">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>947.49</v>
+        <v>953.55</v>
       </c>
     </row>
     <row r="300">
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>2438.26</v>
+        <v>2453.85</v>
       </c>
     </row>
     <row r="301">
@@ -18812,7 +18812,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2146.41</v>
+        <v>2160.14</v>
       </c>
     </row>
     <row r="302">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>2175.17</v>
+        <v>2189.08</v>
       </c>
     </row>
     <row r="303">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>4535.35</v>
+        <v>4564.36</v>
       </c>
     </row>
     <row r="304">
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1618.21</v>
+        <v>1628.56</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>2146.87</v>
+        <v>2160.6</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1271.59</v>
+        <v>1279.72</v>
       </c>
     </row>
     <row r="307">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>9029.92</v>
+        <v>9087.67</v>
       </c>
     </row>
     <row r="308">
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>5568.08</v>
+        <v>5603.7</v>
       </c>
     </row>
     <row r="309">
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>3121.16</v>
+        <v>3141.12</v>
       </c>
     </row>
     <row r="310">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>1657.21</v>
+        <v>1662.42</v>
       </c>
     </row>
     <row r="311">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>987.11</v>
+        <v>990.22</v>
       </c>
     </row>
     <row r="312">
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>5872.45</v>
+        <v>5890.92</v>
       </c>
     </row>
     <row r="313">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>25632.64</v>
+        <v>25713.29</v>
       </c>
     </row>
     <row r="314">
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>986.08</v>
+        <v>989.1799999999999</v>
       </c>
     </row>
     <row r="315">
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>24021.36</v>
+        <v>24096.94</v>
       </c>
     </row>
     <row r="316">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>3281.86</v>
+        <v>3292.18</v>
       </c>
     </row>
     <row r="317">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>8470.27</v>
+        <v>8496.92</v>
       </c>
     </row>
     <row r="318">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>6572.05</v>
+        <v>6592.73</v>
       </c>
     </row>
     <row r="319">
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>10568.98</v>
+        <v>10602.23</v>
       </c>
     </row>
     <row r="320">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>7779.8</v>
+        <v>7804.28</v>
       </c>
     </row>
     <row r="321">
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>7738.82</v>
+        <v>7763.17</v>
       </c>
     </row>
     <row r="322">
@@ -20093,7 +20093,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>5510.01</v>
+        <v>5527.34</v>
       </c>
     </row>
     <row r="323">
@@ -20154,7 +20154,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>32793.37</v>
+        <v>32896.55</v>
       </c>
     </row>
     <row r="324">
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>2505.68</v>
+        <v>2513.56</v>
       </c>
     </row>
     <row r="325">
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>10235.7</v>
+        <v>10267.9</v>
       </c>
     </row>
     <row r="326">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>4382.45</v>
+        <v>4396.24</v>
       </c>
     </row>
     <row r="327">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>1508.07</v>
+        <v>1512.81</v>
       </c>
     </row>
     <row r="328">
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>6224.89</v>
+        <v>6250.69</v>
       </c>
     </row>
     <row r="329">
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>1071.8</v>
+        <v>1076.24</v>
       </c>
     </row>
     <row r="330">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>8584.219999999999</v>
+        <v>8619.799999999999</v>
       </c>
     </row>
     <row r="331">
@@ -20642,7 +20642,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>7506.7</v>
+        <v>7537.81</v>
       </c>
     </row>
     <row r="332">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>4637.59</v>
+        <v>4656.81</v>
       </c>
     </row>
     <row r="333">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>3514.1</v>
+        <v>3528.66</v>
       </c>
     </row>
     <row r="334">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1097.8</v>
+        <v>1102.35</v>
       </c>
     </row>
     <row r="335">
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>3939.08</v>
+        <v>3955.41</v>
       </c>
     </row>
     <row r="336">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>3077.1</v>
+        <v>3089.86</v>
       </c>
     </row>
     <row r="337">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1097.14</v>
+        <v>1101.69</v>
       </c>
     </row>
     <row r="338">
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>11798.92</v>
+        <v>11847.82</v>
       </c>
     </row>
     <row r="339">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>15418.67</v>
+        <v>15482.58</v>
       </c>
     </row>
     <row r="340">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>2831.98</v>
+        <v>2843.71</v>
       </c>
     </row>
     <row r="341">
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>3157.15</v>
+        <v>3170.23</v>
       </c>
     </row>
     <row r="342">
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>11146.06</v>
+        <v>11192.26</v>
       </c>
     </row>
     <row r="343">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>1648.11</v>
+        <v>1654.94</v>
       </c>
     </row>
     <row r="344">
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>4374.93</v>
+        <v>4393.06</v>
       </c>
     </row>
     <row r="345">
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>1678.59</v>
+        <v>1682.07</v>
       </c>
     </row>
     <row r="346">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>8948.35</v>
+        <v>8966.889999999999</v>
       </c>
     </row>
     <row r="347">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>890.8099999999999</v>
+        <v>892.66</v>
       </c>
     </row>
     <row r="348">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>27140.15</v>
+        <v>27196.37</v>
       </c>
     </row>
     <row r="349">
@@ -21740,7 +21740,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>1806.43</v>
+        <v>1810.17</v>
       </c>
     </row>
     <row r="350">
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>45763.83</v>
+        <v>45858.63</v>
       </c>
     </row>
     <row r="351">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>5251.24</v>
+        <v>5262.12</v>
       </c>
     </row>
     <row r="352">
@@ -21923,7 +21923,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>790.21</v>
+        <v>791.85</v>
       </c>
     </row>
     <row r="353">
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>1246.62</v>
+        <v>1249.2</v>
       </c>
     </row>
     <row r="354">
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>5129.44</v>
+        <v>5140.07</v>
       </c>
     </row>
     <row r="355">
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>3424.45</v>
+        <v>3431.55</v>
       </c>
     </row>
     <row r="356">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>2251.74</v>
+        <v>2256.41</v>
       </c>
     </row>
     <row r="357">
@@ -22228,7 +22228,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>1848.98</v>
+        <v>1852.81</v>
       </c>
     </row>
     <row r="358">
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>1110.82</v>
+        <v>1106.04</v>
       </c>
     </row>
     <row r="359">
@@ -22350,7 +22350,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>4289.2</v>
+        <v>4270.78</v>
       </c>
     </row>
     <row r="360">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>3828.83</v>
+        <v>3812.38</v>
       </c>
     </row>
     <row r="361">
@@ -22472,7 +22472,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>1479.83</v>
+        <v>1473.47</v>
       </c>
     </row>
     <row r="362">
@@ -22533,7 +22533,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>939.53</v>
+        <v>935.5</v>
       </c>
     </row>
     <row r="363">
@@ -22594,7 +22594,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>4724.77</v>
+        <v>4704.47</v>
       </c>
     </row>
     <row r="364">
@@ -22655,7 +22655,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>2074.27</v>
+        <v>2065.36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/abr-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/abr-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17705,7 +17705,7 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20622,7 +20622,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20683,7 +20683,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -21537,7 +21537,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21720,7 +21720,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21964,7 +21964,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22513,7 +22513,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/abr-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/abr-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M364"/>
+  <dimension ref="A1:M365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (V)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Superintendencia de Servicios Sanitarios</t>
+          <t>SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Feria Internacional del Aire y del Espacio</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CDP Ovalle</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (V)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICAC</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (V)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (V)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SAMU</t>
+          <t>Centro Metropolitano de Atención Prehospitalaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DIRECCION DE SEGURIDAD Y OPERACIONES MARITIMAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (T)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (V)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>BUQUE ESCUELA ESMERALDA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEGURIDAD INDUSTRIAL SPA </t>
+          <t xml:space="preserve">Seguridad Industrial SPA </t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dirección General de Gendarmería de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (V)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE QUILLÓN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE QUILLÓN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SEREMI IX</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14767,7 +14767,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16150,7 +16150,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -16719,7 +16719,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17750,7 +17750,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar Social</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18238,7 +18238,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmería</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18736,7 +18736,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -18787,7 +18787,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmería</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -18797,7 +18797,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19031,7 +19031,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19153,7 +19153,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19275,7 +19275,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yumbel - Depto. Salud</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19336,7 +19336,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Gendarmeria de Chile Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19773,7 +19773,7 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
@@ -19885,7 +19885,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -20007,7 +20007,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20068,7 +20068,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20190,7 +20190,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -20373,7 +20373,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del Centro de Cumpli</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -20800,7 +20800,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -20912,7 +20912,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21349,7 +21349,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -21532,7 +21532,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (T)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -21807,7 +21807,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>529318-73-CM26</t>
+          <t>4036-226-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -21827,32 +21827,32 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>61.102.008-2</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>DEPTO HABITABILIDAD COMANDANCIA EN JEFE DE 1 Z. N.</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>CRISTIAN</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>77.054.796-2</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K351" t="inlineStr"/>
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>5262.12</v>
+        <v>1852.81</v>
       </c>
     </row>
     <row r="352">
@@ -22173,7 +22173,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>4036-226-CM26</t>
+          <t>529318-73-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -22193,32 +22193,32 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>61.102.008-2</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>CRISTIAN</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.054.796-2</t>
         </is>
       </c>
       <c r="K357" t="inlineStr"/>
@@ -22228,13 +22228,13 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>1852.81</v>
+        <v>5262.12</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1953-746-CM26</t>
+          <t>1289422-68-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -22259,27 +22259,27 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.004.024-1</t>
+          <t>73.060.100-K</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>CORPORACION CULTURAL DE LO BARNECHEA</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.183.081-3</t>
         </is>
       </c>
       <c r="K358" t="inlineStr"/>
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>1106.04</v>
+        <v>2065.36</v>
       </c>
     </row>
     <row r="359">
@@ -22600,7 +22600,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1289422-68-CM26</t>
+          <t>1953-746-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -22625,27 +22625,27 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>73.060.100-K</t>
+          <t>61.004.024-1</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL DE LO BARNECHEA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>76.183.081-3</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K364" t="inlineStr"/>
@@ -22655,7 +22655,68 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>2065.36</v>
+        <v>1106.04</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>545774-19-CM26</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>69.070.800-0</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>COMERCIAL RAFF SPA</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>77.303.388-9</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="n">
+        <v>49674.28</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/abr-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/abr-2026.xlsx
@@ -623,7 +623,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1798,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1863,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2538,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2847,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2912,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +2977,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3042,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3290,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3355,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3420,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3546,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3672,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3737,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3863,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4111,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4237,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4424,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4794,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4920,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +4985,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5172,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5237,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5424,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5672,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5798,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6107,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6172,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6420,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6546,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7038,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7164,11 @@
           <t>77.714.558-4</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7290,11 @@
           <t>77.303.388-9</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7355,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7847,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8217,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8282,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8408,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8534,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8782,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8847,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +8973,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9282,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9347,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9412,11 @@
           <t>77.787.617-1</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9538,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9664,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +9973,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10343,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10469,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10534,11 @@
           <t>77.714.558-4</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10599,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +10969,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11034,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11160,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11347,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11473,11 @@
           <t>77.303.388-9</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11599,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11664,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +11790,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +11916,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +11981,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12107,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12172,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12298,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12485,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12550,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12676,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12741,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12867,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +12993,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13119,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13306,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13493,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13558,11 @@
           <t>77.303.388-9</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13623,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13688,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13753,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14062,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14127,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14497,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +14806,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +14932,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15180,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15306,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15615,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +15680,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +15867,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +15932,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +15997,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16123,11 @@
           <t>76.698.741-9</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16188,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16436,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16562,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +16688,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +16997,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17367,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17493,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +17680,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +17806,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +17993,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17768,7 +18184,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17829,7 +18249,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18012,7 +18436,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18439,7 +18867,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18500,7 +18932,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18622,7 +19058,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18683,7 +19123,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19293,7 +19737,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19476,7 +19924,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19659,7 +20111,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20513,7 +20969,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20574,7 +21034,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20635,7 +21099,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20696,7 +21164,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21001,7 +21473,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21123,7 +21599,11 @@
           <t>77.724.409-4</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21489,7 +21969,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21550,7 +22034,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21672,7 +22160,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21794,7 +22286,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22526,7 +23022,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22587,7 +23087,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22709,7 +23213,11 @@
           <t>77.303.388-9</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/abr-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/abr-2026.xlsx
@@ -7229,7 +7229,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7786,7 +7790,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8034,7 +8042,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9790,7 +9802,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13940,7 +13956,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15119,7 +15139,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17123,7 +17147,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/abr-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/abr-2026.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -17932,7 +17932,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -20969,7 +20969,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
